--- a/ATL_OPS_EF_Librerie_v1.xlsx
+++ b/ATL_OPS_EF_Librerie_v1.xlsx
@@ -21,6 +21,8 @@
     <sheet name="11_Tier_validazione" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="12_Gaps" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="13_Legenda" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14_Verifica_fonti" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15_Conflitti" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_Schema_canonico'!$A$4:$D$54</definedName>
@@ -30,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_LIB-04_CC-FOREST'!$A$2:$BA$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_LIB-05_CCF'!$A$2:$BA$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_LIB-06_PCF'!$A$2:$BA$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_Gaps'!$A$4:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_Gaps'!$A$4:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -693,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -721,7 +723,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1045,7 +1046,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -1057,7 +1057,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -1088,9 +1087,20 @@
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="26" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>VERIFICA DI FONTE ESEGUITA IL 21/08/2026 — ESITO: NON COMPLETABILE IN QUESTO AMBIENTE. I documenti primari sono stati localizzati (foglio 14_Verifica_fonti) ma non sono scaricabili: la policy di egress blocca arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it ed eur-lex.europa.eu (GAP-018). Nessun valore e' stato estratto da fonti secondarie e nessun record e' stato promosso: tutti restano status = draft. Due conflitti aperti nel foglio 15_Conflitti. Da verificare con priorita': il D.M. MASE 21 luglio 2025, che se confermato ridefinisce la base normativa di LIB-01 (VF-004, escalation §14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A18:I21"/>
     <mergeCell ref="A14:I16"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -1775,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1845,12 +1855,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Decreto certificati bianchi 2025: modifica di vita utile degli interventi e regole di raggruppamento dei progetti</t>
+          <t>Decreto certificati bianchi 2025: modifica di vita utile degli interventi e regole di raggruppamento dei progetti. LEAD IDENTIFICATO (da fonti secondarie, da confermare): D.M. MASE 21 luglio 2025, GU n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025. Vedi VF-004.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verificare il testo in Gazzetta Ufficiale e mappare tutti i record impattati prima di consolidare LIB-01. Non recepire da fonti secondarie.</t>
+          <t>Verificare il testo in Gazzetta Ufficiale e mappare tutti i record impattati prima di consolidare LIB-01. Non recepire da fonti secondarie. ESCALATION A TOBIA: se confermato, l'aggiornamento e' strutturale e non di singoli record (§14).</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1877,7 +1887,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>legal_reference incompleto per il coefficiente gas naturale 0,000836 tep/Sm3</t>
+          <t>legal_reference incompleto per il coefficiente gas naturale 0,000836 tep/Sm3. Ricerca eseguita: l'atto che fissa il coefficiente NON e' stato identificato. Il valore compare in moduli applicativi di amministrazioni pubbliche, che non sono fonte primaria. Vedi VF-002.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2376,8 +2386,72 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>GAP-018</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Trasversale</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Accesso alle fonti primarie bloccato dalla policy di egress dell'ambiente di esecuzione: arera.it, gazzettaufficiale.it, gse.it, mimit.gov.it, mase.gov.it, eur-lex.europa.eu risultano tutti non raggiungibili in fetch diretto.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>La verifica di fonte non e' completabile in questo ambiente. Due rimedi alternativi: (a) autorizzare in allowlist i domini delle fonti primarie; (b) scaricamento manuale dei documenti da parte di una persona e deposito in sources/&lt;org&gt;/&lt;documento&gt;_&lt;edizione&gt;/ con hash. Senza uno dei due, nessun record puo' superare il gate 2.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Blocca l'intera pipeline di ingestione: nessun record promuovibile oltre draft</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Aperta — decisione tecnica/organizzativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>GAP-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>LIB-01 / LIB-02</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Definizione di 1 tep: coesistenza di 41,860 GJ (regime nazionale TEE) e 41,868 GJ (IEA/OCSE, direttiva 2012/27/UE).</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Registrato come CONF-002. Richiede la gerarchia di fonte di Garbin e la decisione se esporre due record distinti con ambiti di applicabilita' dichiarati. Nessuna scelta autonoma dell'agent.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Riproducibilita' del calcolo in verifica di terza parte: due definizioni danno risultati non identici</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Aperta — richiede gerarchia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F21"/>
+  <autoFilter ref="A4:F23"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -2748,6 +2822,499 @@
     <mergeCell ref="A28:C30"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Verifica di fonte — stato al 21/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ricerca eseguita per LOCALIZZARE i documenti primari. Nessun valore e' stato estratto da fonti secondarie: §1 vieta blog, articoli divulgativi, siti di ESCo e output di modelli linguistici come fonte. Tutti i record restano status = draft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Record / gap</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Dato dichiarato in CLAUDE.md</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Documento primario candidato</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Locatore (da fetchare quando l'accesso sara' consentito)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Cosa estrarre</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Stato accesso</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Esito della verifica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>VF-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>LIB01-EE-PRIM-0001</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0,187 x 10^-3 tep/kWh (energia elettrica -&gt; energia primaria)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Delibera AEEG (ora ARERA) EEN 3/08 — 'Aggiornamento del fattore di conversione dei kWh in tonnellate equivalenti di petrolio connesso al meccanismo dei titoli di efficienza energetica'</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>ARERA</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.arera.it/atti-e-provvedimenti/dettaglio/08/003-08een</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Valore verbatim; articolo/comma; allegato e tabella; pagina; data di adozione; data di entrata in vigore; testo integrale per hash SHA-256</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>BLOCCATO — policy di egress</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Titolo del provvedimento coerente con quello citato in CLAUDE.md. La DATA di adozione risulta discordante tra fonti secondarie (20 / 28 / 31 marzo 2008): vedi CONF-001. Il valore non e' confermato: la conferma richiede il testo del provvedimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>VF-002</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>LIB01-GN-PRIM-0002</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0,000836 tep/Sm3 (gas naturale)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Atto non ancora identificato. Ipotesi da verificare in ordine: (a) Delibera EEN 3/08 e successivi aggiornamenti; (b) Allegato A alla delibera EEN 9/10 e successive Linee guida ARERA; (c) tabella dei coefficienti nella Guida Operativa GSE vigente; (d) D.M. 20 luglio 2004</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ARERA / GSE / MASE</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arera.it/fileadmin/allegati/docs/10/009-10eenallA_ti.pdf ; https://www.gse.it/servizi-per-te/efficienza-energetica/certificati-bianchi/documenti</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Identificare l'atto che fissa il coefficiente; poi valore verbatim, tabella, pagina, vigenza</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>BLOCCATO — policy di egress</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Il valore circola in moduli di conversione di amministrazioni pubbliche, che NON sono fonte primaria: sono applicazioni di un coefficiente stabilito altrove. Resta GAP-002: l'atto non e' identificato, il record non supera i gate 2 e 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>VF-003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>LIB02-TEP-GJ-0001</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1 tep = 41,860 GJ (identita' tep -&gt; GJ)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>D.M. Ministero delle Attivita' Produttive 20 luglio 2004 (indicato da fonti secondarie come l'atto che fissa 1 tep = 41,860 GJ per il meccanismo TEE)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>MASE (gia' Ministero Attivita' Produttive)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gazzettaufficiale.it (ricerca per D.M. 20 luglio 2004)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Testo che fissa il fattore; articolo; allegato; pagina di GU; data di entrata in vigore</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>BLOCCATO — policy di egress</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CONFLITTO APERTO con la definizione IEA/OCSE e con la direttiva 2012/27/UE (41,868 GJ): vedi CONF-002. Non risolto dall'agent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>VF-004</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>GAP-001</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Decreto certificati bianchi 2025 — vita utile e raggruppamento progetti</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>D.M. MASE 21 luglio 2025 (indicato da fonti secondarie come pubblicato in Gazzetta Ufficiale n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025). Guida Operativa attuativa approvata con decreto direttoriale (n. 203 del 28 luglio 2026 secondo fonti secondarie)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>MASE / GSE</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.gazzettaufficiale.it (GU Serie Generale n. 211 dell'11/09/2025) ; https://www.gse.it/servizi-per-te/efficienza-energetica/certificati-bianchi/documenti</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Testo integrale del decreto e degli allegati tecnici; articoli su vita utile, metodi di valutazione (consuntivo / standardizzato / semplificato), progetti aggregati; mappatura dei record LIB-01 impattati</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>BLOCCATO — policy di egress</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>ESCALATION A TOBIA (§14): se confermato, questo decreto ridefinisce la base normativa dell'intera LIB-01 e non e' un aggiornamento di singoli record. Nessun consolidamento di LIB-01 prima della verifica in Gazzetta Ufficiale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VF-005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Trasversale</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Coefficienti per gli altri vettori ammessi; parametri CAR; vita utile; coefficienti di durabilita'; soglie di accesso</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Guida Operativa GSE vigente e allegati (chiarimenti, guide settoriali, chiarimenti sulla Tabella 1 degli interventi)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>GSE</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gse.it/servizi-per-te/efficienza-energetica/certificati-bianchi/documenti</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Tabelle complete dei coefficienti, con edizione e data di pubblicazione</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>BLOCCATO — policy di egress</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Copertura non avviata: GAP-004. La verifica non e' iniziabile senza accesso al sito GSE.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Conflitti tra fonti — non risolti dall'agent (§11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entrambi i valori sono riportati con la loro provenienza. La gerarchia di fonte va registrata da Garbin in taxonomy/source_hierarchy.yaml prima di qualunque scelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Chiave in conflitto</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Valore A (con provenienza)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Valore B (con provenienza)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Natura del conflitto</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Impatto</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Decisione richiesta</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CONF-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Data di adozione della delibera AEEG EEN 3/08</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>20 marzo 2008</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>28 marzo 2008 / 31 marzo 2008</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Fonti secondarie discordanti (moduli di conversione, portali di settore, enciclopedie collaborative). Nessuna e' fonte primaria.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Il campo legal_reference di LIB-01 richiede la data di entrata in vigore. Una data errata rende il riferimento normativo non verificabile in audit di terza parte.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Risolvibile SOLO leggendo il provvedimento sul sito ARERA. Non richiede una decisione di gerarchia: richiede accesso alla fonte.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Aperto — bloccato da accesso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>CONF-002</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Contenuto energetico di 1 tep (identita' tep -&gt; GJ -&gt; kWh_th)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>1 tep = 41,860 GJ  -&gt;  11.627,8 kWh_th (arrotondato a 11.628). Provenienza indicata: D.M. 20 luglio 2004, regime TEE italiano. DA VERIFICARE IN GU.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1 tep = 41,868 GJ  -&gt;  11.630 kWh_th. Provenienza indicata: definizione IEA/OCSE, ripresa dalla direttiva 2012/27/UE. DA VERIFICARE IN EUR-LEX.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Conflitto di regime, non di misura: due definizioni convenzionali coesistenti, una nazionale e una internazionale. Scarto 0,019% sul contenuto energetico.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Numericamente marginale, ma NON trascurabile per la riproducibilita': un auditor che ricalcola con 41,868 non riproduce un risparmio calcolato con 41,860. Impatta anche la collocazione del record (LIB-01 regime TEE vs LIB-02 identita' fisica).</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>DECISIONE A GARBIN. Il §4 stabilisce che per LIB-01 vale solo il diritto nazionale italiano: se il record e' TEE, prevale il valore nazionale. Resta da decidere se LIB-02 esponga un secondo record per uso extra-TEE, e con quale gerarchia. L'agent non sceglie.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Aperto — richiede gerarchia</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4498,7 +5065,7 @@
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="4" t="inlineStr">
         <is>
-          <t>ATTENZIONE ASIMMETRIA (§3 LIB-01): questo valore incorpora il rendimento medio del parco termoelettrico nazionale (~46%) — e' un fattore di ENERGIA PRIMARIA, non un'identita' fisica. Non trattarlo come oggetto omogeneo rispetto al tep-&gt;kWh_th. Valore riportato in CLAUDE.md come verificato ad agosto 2026 e da riconfermare in fonte primaria prima del rilascio.</t>
+          <t>ATTENZIONE ASIMMETRIA (§3 LIB-01): questo valore incorpora il rendimento medio del parco termoelettrico nazionale (~46%) — e' un fattore di ENERGIA PRIMARIA, non un'identita' fisica. Non trattarlo come oggetto omogeneo rispetto al tep-&gt;kWh_th. Valore riportato in CLAUDE.md come verificato ad agosto 2026 e da riconfermare in fonte primaria prima del rilascio.  || VERIFICA DI FONTE 21/08/2026 (VF-001): individuato il provvedimento ARERA corrispondente al titolo citato, ma il sito e' inaccessibile (GAP-018) e la data di adozione risulta discordante tra fonti secondarie (CONF-001). Il valore NON e' confermato in fonte primaria: il record resta draft.</t>
         </is>
       </c>
       <c r="AZ5" s="4" t="inlineStr"/>
@@ -4727,7 +5294,7 @@
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr">
         <is>
-          <t>La fonte indicata in CLAUDE.md ('Tabelle di conversione ufficiali') non e' localizzabile a documento/edizione/tabella/pagina. Il record NON supera il gate 2 (provenienza completa) ne' il gate 10: non entra in un pacchetto di validazione fino a identificazione dell'atto.</t>
+          <t>La fonte indicata in CLAUDE.md ('Tabelle di conversione ufficiali') non e' localizzabile a documento/edizione/tabella/pagina. Il record NON supera il gate 2 (provenienza completa) ne' il gate 10: non entra in un pacchetto di validazione fino a identificazione dell'atto.  || VERIFICA DI FONTE 21/08/2026 (VF-002): ricerca eseguita, atto NON identificato. Il coefficiente compare solo in moduli applicativi di enti pubblici, che sono applicazioni e non fonte primaria. Il record resta draft e fuori pacchetto.</t>
         </is>
       </c>
       <c r="AZ6" s="4" t="inlineStr"/>
@@ -5403,7 +5970,7 @@
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="4" t="inlineStr">
         <is>
-          <t>DECISIONE DI CLASSIFICAZIONE DA CONFERMARE A GARBIN: CLAUDE.md cita questo valore nella tabella di riferimento di LIB-01, ma §3 LIB-02 assegna a LIB-02 la catena tep&lt;-&gt;GJ&lt;-&gt;kWh&lt;-&gt;Sm3 come identita' pura. Collocato qui in via provvisoria. L'11.628 kWh_th/tep non incorpora alcun rendimento: non e' omogeneo allo 0,187 tep/kWh di LIB-01.</t>
+          <t>DECISIONE DI CLASSIFICAZIONE DA CONFERMARE A GARBIN: CLAUDE.md cita questo valore nella tabella di riferimento di LIB-01, ma §3 LIB-02 assegna a LIB-02 la catena tep&lt;-&gt;GJ&lt;-&gt;kWh&lt;-&gt;Sm3 come identita' pura. Collocato qui in via provvisoria. L'11.628 kWh_th/tep non incorpora alcun rendimento: non e' omogeneo allo 0,187 tep/kWh di LIB-01.  || VERIFICA DI FONTE 21/08/2026 (VF-003): candidato primario D.M. 20 luglio 2004 (da confermare in GU). CONFLITTO CONF-002 con la definizione IEA/OCSE e con la direttiva 2012/27/UE (41,868 GJ -&gt; 11.630 kWh_th). Non risolto: decisione di gerarchia a Garbin.</t>
         </is>
       </c>
       <c r="AZ5" s="4" t="inlineStr"/>

--- a/ATL_OPS_EF_Librerie_v1.xlsx
+++ b/ATL_OPS_EF_Librerie_v1.xlsx
@@ -1093,16 +1093,40 @@
           <t>VERIFICA DI FONTE ESEGUITA IL 21/08/2026 — ESITO: NON COMPLETABILE IN QUESTO AMBIENTE. I documenti primari sono stati localizzati (foglio 14_Verifica_fonti) ma non sono scaricabili: la policy di egress blocca arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it ed eur-lex.europa.eu (GAP-018). Nessun valore e' stato estratto da fonti secondarie e nessun record e' stato promosso: tutti restano status = draft. Due conflitti aperti nel foglio 15_Conflitti. Da verificare con priorita': il D.M. MASE 21 luglio 2025, che se confermato ridefinisce la base normativa di LIB-01 (VF-004, escalation §14).</t>
         </is>
       </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n"/>
+      <c r="I19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n"/>
+      <c r="I20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="26" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A18:I21"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A14:I16"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2404,7 +2428,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>La verifica di fonte non e' completabile in questo ambiente. Due rimedi alternativi: (a) autorizzare in allowlist i domini delle fonti primarie; (b) scaricamento manuale dei documenti da parte di una persona e deposito in sources/&lt;org&gt;/&lt;documento&gt;_&lt;edizione&gt;/ con hash. Senza uno dei due, nessun record puo' superare il gate 2.</t>
+          <t>RIMEDIO SCELTO: allowlist dei domini di fonte primaria. Elenco completo, per tier e per libreria, in docs/ATL_OPS_EF_Allowlist_fonti_v1.md. La policy di rete e' attributo dell'environment (Default - trusted network access) e non e' modificabile dall'interno di una sessione: va aggiornata nelle impostazioni dell'environment su claude.ai/code, poi serve una NUOVA sessione perche' la policy si applica all'avvio del container. Tier 1 bloccante: arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it, eur-lex.europa.eu (con wildcard sui sottodomini, altrimenti la pagina indice si scarica e l'allegato no).</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2414,7 +2438,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Aperta — decisione tecnica/organizzativa</t>
+          <t>In lavorazione — allowlist da applicare all'environment</t>
         </is>
       </c>
     </row>

--- a/ATL_OPS_EF_Librerie_v1.xlsx
+++ b/ATL_OPS_EF_Librerie_v1.xlsx
@@ -23,6 +23,10 @@
     <sheet name="13_Legenda" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="14_Verifica_fonti" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="15_Conflitti" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_Allowlist_domini" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_Domini_esclusi" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18_Piano_lavoro" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="19_Changelog_curazione" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_Schema_canonico'!$A$4:$D$54</definedName>
@@ -33,6 +37,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_LIB-05_CCF'!$A$2:$BA$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_LIB-06_PCF'!$A$2:$BA$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_Gaps'!$A$4:$F$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_Verifica_fonti'!$A$4:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'16_Allowlist_domini'!$A$4:$F$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,7 +100,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +129,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="006FBF7A"/>
       </patternFill>
     </fill>
@@ -136,18 +147,8 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -169,104 +170,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -296,40 +204,34 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -695,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -704,7 +606,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
@@ -719,11 +621,11 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Curata internamente. Nessun record validato: la firma del CSO non e' stata apposta. Struttura conforme a CLAUDE.md v2 (ATL_OPS_AgentEF_IstruzioniClaudeCode_v2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Curata internamente. Nessun record validato: la firma del CSO non e' stata apposta. Conforme a CLAUDE.md v2 (ATL_OPS_AgentEF_IstruzioniClaudeCode_v2). Aggiornato al 21/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>library_id</t>
@@ -756,7 +658,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Record bozza presenti</t>
+          <t>Record bozza</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1060,73 +962,37 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Nessun valore e' stato stimato, interpolato o derivato. Le celle vuote nei fogli libreria sono lacune non colmate, non dati mancanti per distrazione: la lacuna dichiarata e' un deliverable (§1). I record presenti hanno provenienza incompleta e sono marcati status = draft: vanno riconfermati in fonte primaria prima di qualunque uso in calcolo.</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="21" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="I15" s="23" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="26" t="n"/>
-    </row>
+          <t>STATO AL 21/08/2026. Nessun valore e' stato stimato, interpolato o derivato. I soli record presenti sono i tre coefficienti che CLAUDE.md riporta esplicitamente, in status = draft, con i campi di provenienza non localizzabili marcati [DA VERIFICARE IN FONTE PRIMARIA]: non superano il gate 2 e non sono utilizzabili in calcolo. LIB-03…LIB-06 sono template vuoti: le celle vuote sono lacune dichiarate (foglio 12_Gaps), non dimenticanze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>VERIFICA DI FONTE ESEGUITA IL 21/08/2026 — ESITO: NON COMPLETABILE IN QUESTO AMBIENTE. I documenti primari sono stati localizzati (foglio 14_Verifica_fonti) ma non sono scaricabili: la policy di egress blocca arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it ed eur-lex.europa.eu (GAP-018). Nessun valore e' stato estratto da fonti secondarie e nessun record e' stato promosso: tutti restano status = draft. Due conflitti aperti nel foglio 15_Conflitti. Da verificare con priorita': il D.M. MASE 21 luglio 2025, che se confermato ridefinisce la base normativa di LIB-01 (VF-004, escalation §14).</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="21" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="I19" s="23" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n"/>
-      <c r="I20" s="23" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="26" t="n"/>
-    </row>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>VERIFICA DI FONTE ESEGUITA, NON COMPLETABILE IN QUESTO AMBIENTE. I documenti primari sono stati localizzati (14_Verifica_fonti) ma non scaricabili: la policy di egress blocca arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it, eur-lex.europa.eu (GAP-018). Rimedio in 16_Allowlist_domini. Due conflitti aperti in 15_Conflitti. Priorita' assoluta: il D.M. MASE 21 luglio 2025, che se confermato ridefinisce la base normativa di tutta LIB-01 (VF-004, escalation §14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>GUIDA AI FOGLI. 01 schema dei 50 campi · 02-07 le sei librerie · 08 licenze · 09 i 14 gate di qualita' · 10 gate trasversali G1-G3 · 11 tier di validazione e contenuto del pacchetto · 12 lacune aperte · 13 legenda di compilazione · 14 verifica di fonte · 15 conflitti non risolti · 16 allowlist dei domini · 17 domini esclusi · 18 piano di lavoro · 19 registro dello sforzo di curazione (§15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A14:I16"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A22:I24"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A18:I21"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A14:I16"/>
+    <mergeCell ref="A18:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1138,13 +1004,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1161,7 +1028,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -1180,6 +1047,11 @@
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Librerie interessate</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Stato al 21/08/2026</t>
         </is>
       </c>
     </row>
@@ -1202,6 +1074,11 @@
           <t>Tutte</t>
         </is>
       </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Eseguibile</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1222,6 +1099,11 @@
           <t>Tutte</t>
         </is>
       </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>BLOCCATO — GAP-018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1242,6 +1124,11 @@
           <t>Tutte</t>
         </is>
       </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>BLOCCATO — manca units.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1262,6 +1149,11 @@
           <t>Tutte</t>
         </is>
       </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>BLOCCATO — manca plausibility_ranges.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1282,6 +1174,11 @@
           <t>Tutte</t>
         </is>
       </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Non applicabile: nessuna versione precedente</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1294,12 +1191,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Stessa chiave (attivita' + geografia + anno + confine di sistema) da fonti diverse -&gt; conflitti.md. Mai risolto dall'agent.</t>
+          <t>Stessa chiave (attivita' + geografia + anno + confine di sistema) da fonti diverse -&gt; 15_Conflitti. Mai risolto dall'agent.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Tutte</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Eseguibile — 2 conflitti aperti</t>
         </is>
       </c>
     </row>
@@ -1322,6 +1224,11 @@
           <t>LIB-05, LIB-06</t>
         </is>
       </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Non applicabile: nessun record</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1342,6 +1249,11 @@
           <t>LIB-05</t>
         </is>
       </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Assenza dichiarata: GAP-009</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1362,6 +1274,11 @@
           <t>LIB-03, LIB-04, LIB-06</t>
         </is>
       </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Non applicabile: nessun record</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1382,6 +1299,11 @@
           <t>LIB-01</t>
         </is>
       </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>FALLITO su LIB01-GN-PRIM-0002</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1402,6 +1324,11 @@
           <t>LIB-03, LIB-04</t>
         </is>
       </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Non applicabile: nessun record</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1422,6 +1349,11 @@
           <t>LIB-04</t>
         </is>
       </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Non applicabile: nessun record</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1442,6 +1374,11 @@
           <t>LIB-01, LIB-02</t>
         </is>
       </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Eseguibile — vedi GAP-003</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1462,11 +1399,26 @@
           <t>Tutte</t>
         </is>
       </c>
-    </row>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>BLOCCATO — nessun hash calcolabile senza documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Cinque gate su quattordici sono bloccati dall'assenza di accesso alle fonti primarie o dei file di tassonomia, non da un difetto dei record. Il gate 10 e' invece un fallimento reale su un record: LIB01-GN-PRIM-0002 non ha legal_reference perche' l'atto non e' stato identificato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1478,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1502,7 +1454,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1610,10 +1562,20 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>APPLICAZIONE CORRENTE DI G3. Il caso concreto e' il valore di 12.500 kWh_th/tep circolante internamente: corrisponde a 11.628 diviso un rendimento di riferimento di circa 0,93. Non e' un fattore di conversione, e' un'assunzione di rendimento. Non e' stato inserito come record: e' GAP-003. Inserirlo come costante sarebbe esattamente cio' che G3 esiste per impedire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1625,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1609,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Tier</t>
@@ -1722,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Elemento</t>
@@ -1794,10 +1756,20 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>STATO: NESSUN PACCHETTO COMPONIBILE. I tre record esistenti sono tutti T1 (LIB-01 e manual_transcription), ma nessuno supera il gate 2: un pacchetto composto ora chiederebbe a Garbin di validare valori privi di provenienza, cioe' di firmare cio' che il §1 vieta di produrre. Il pacchetto si compone dopo la verifica di fonte, non prima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A18:C20"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1834,7 +1806,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1879,12 +1851,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Decreto certificati bianchi 2025: modifica di vita utile degli interventi e regole di raggruppamento dei progetti. LEAD IDENTIFICATO (da fonti secondarie, da confermare): D.M. MASE 21 luglio 2025, GU n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025. Vedi VF-004.</t>
+          <t>Decreto certificati bianchi 2025: modifica di vita utile degli interventi e regole di raggruppamento dei progetti. LEAD INDIVIDUATO (fonti secondarie, da confermare): D.M. MASE 21 luglio 2025, GU n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025. Vedi VF-004.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Verificare il testo in Gazzetta Ufficiale e mappare tutti i record impattati prima di consolidare LIB-01. Non recepire da fonti secondarie. ESCALATION A TOBIA: se confermato, l'aggiornamento e' strutturale e non di singoli record (§14).</t>
+          <t>Verificare il testo in Gazzetta Ufficiale e mappare tutti i record impattati prima di consolidare LIB-01. Non recepire da fonti secondarie. ESCALATION A TOBIA: se confermato l'aggiornamento e' strutturale, non di singoli record (§14).</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1894,7 +1866,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Aperta — segnalata in CLAUDE.md §3</t>
+          <t>Aperta — priorita' 1</t>
         </is>
       </c>
     </row>
@@ -1911,17 +1883,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>legal_reference incompleto per il coefficiente gas naturale 0,000836 tep/Sm3. Ricerca eseguita: l'atto che fissa il coefficiente NON e' stato identificato. Il valore compare in moduli applicativi di amministrazioni pubbliche, che non sono fonte primaria. Vedi VF-002.</t>
+          <t>legal_reference incompleto per il coefficiente gas naturale 0,000836 tep/Sm3. Ricerca eseguita: l'atto che lo fissa NON e' stato identificato. Il valore compare in moduli applicativi di enti pubblici, che non sono fonte primaria. Vedi VF-002.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>La dicitura 'Tabelle di conversione ufficiali' non e' localizzabile a documento/edizione/tabella/pagina: identificare l'atto.</t>
+          <t>Identificare l'atto. Se non esiste un atto che fissa il coefficiente, dichiarare la lacuna: e' un esito legittimo.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Il record non supera i gate 2 e 10: non entra in pacchetto</t>
+          <t>Il record non supera i gate 2 e 10: fuori pacchetto</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1948,7 +1920,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>NON inserito come record: e' un'assunzione di rendimento senza fonte primaria identificata. Va reperito nella scheda/guida GSE applicabile e censito come reference_parameter separato, mai incorporato in un coefficiente di conversione.</t>
+          <t>NON inserito come record: e' un'assunzione di rendimento senza fonte primaria identificata. Va reperito nella scheda/guida GSE applicabile e censito come reference_parameter separato, mai incorporato in un coefficiente di conversione (gate G3).</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1980,12 +1952,12 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Copertura non avviata.</t>
+          <t>Copertura non avviata. Fonte: Guida Operativa GSE vigente e allegati (VF-005).</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>LIB-01 non utilizzabile in produzione oltre i vettori elettrico e gas</t>
+          <t>LIB-01 non utilizzabile oltre i vettori elettrico e gas</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -2017,7 +1989,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Diagnosi UNI CEI 11339 e Digital Twin non coperti dalla libreria</t>
+          <t>Diagnosi UNI CEI 11339 e Digital Twin non coperti</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2086,7 +2058,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Aperta — dipende da interlocuzione CREA</t>
+          <t>Aperta — dipende da CREA</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2122,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Aperta</t>
+          <t>Aperta — assenza dichiarata</t>
         </is>
       </c>
     </row>
@@ -2172,12 +2144,12 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Copertura non avviata. Fonte gerarchicamente prevalente per l'Italia: inventario nazionale.</t>
+          <t>Copertura non avviata. Fonte gerarchicamente prevalente per l'Italia: inventario nazionale ISPRA.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Nessun inventario di organizzazione producibile dalla libreria</t>
+          <t>Nessun inventario di organizzazione producibile</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -2246,7 +2218,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Aperta — richiede decisione di Tobia</t>
+          <t>Aperta — decisione di Tobia</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2336,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Con il portafoglio attuale l'insieme e' determinabile manualmente: CLAUDE.md §9 prescrive di farlo ora, finche' e' possibile.</t>
+          <t>Con il portafoglio attuale l'insieme e' determinabile manualmente: il §9 prescrive di farlo ora, finche' e' possibile.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2396,17 +2368,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Ore, record lavorati, fonti verificate, conflitti risolti. Ricostruirlo a posteriori non e' possibile (§15): e' la prova d'investimento per il diritto sui generis sulla banca dati.</t>
+          <t>Avviato nel foglio 19_Changelog_curazione. Da riversare in docs/changelog.md e mantenere. Ore, record lavorati, fonti verificate, conflitti: ricostruirlo a posteriori non e' possibile (§15).</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Finestra che si chiude: ogni giorno senza registro e' perso</t>
+          <t>Prova d'investimento per il diritto sui generis sulla banca dati</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Aperta — priorita' immediata</t>
+          <t>In lavorazione</t>
         </is>
       </c>
     </row>
@@ -2423,22 +2395,22 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Accesso alle fonti primarie bloccato dalla policy di egress dell'ambiente di esecuzione: arera.it, gazzettaufficiale.it, gse.it, mimit.gov.it, mase.gov.it, eur-lex.europa.eu risultano tutti non raggiungibili in fetch diretto.</t>
+          <t>Accesso alle fonti primarie bloccato dalla policy di egress: arera.it, gazzettaufficiale.it, gse.it, mimit.gov.it, mase.gov.it, eur-lex.europa.eu non raggiungibili in fetch diretto.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>RIMEDIO SCELTO: allowlist dei domini di fonte primaria. Elenco completo, per tier e per libreria, in docs/ATL_OPS_EF_Allowlist_fonti_v1.md. La policy di rete e' attributo dell'environment (Default - trusted network access) e non e' modificabile dall'interno di una sessione: va aggiornata nelle impostazioni dell'environment su claude.ai/code, poi serve una NUOVA sessione perche' la policy si applica all'avvio del container. Tier 1 bloccante: arera.it, gazzettaufficiale.it, gse.it, mase.gov.it, mimit.gov.it, eur-lex.europa.eu (con wildcard sui sottodomini, altrimenti la pagina indice si scarica e l'allegato no).</t>
+          <t>RIMEDIO SCELTO: allowlist dei domini (foglio 16_Allowlist_domini e docs/ATL_OPS_EF_Allowlist_fonti_v1.md). La policy di rete e' attributo dell'environment e non e' modificabile da dentro una sessione: va aggiornata su claude.ai/code, poi serve una NUOVA sessione. Usare wildcard sui sottodomini.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Blocca l'intera pipeline di ingestione: nessun record promuovibile oltre draft</t>
+          <t>Blocca l'intera pipeline: nessun record promuovibile oltre draft</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>In lavorazione — allowlist da applicare all'environment</t>
+          <t>In lavorazione — allowlist da applicare</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2437,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Riproducibilita' del calcolo in verifica di terza parte: due definizioni danno risultati non identici</t>
+          <t>Riproducibilita' in verifica di terza parte: due definizioni danno risultati non identici</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2490,7 +2462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2512,7 +2484,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Elemento</t>
@@ -2624,228 +2596,232 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Non stima, non interpola, non media, non estrapola, non applica rendimenti o COP per riportare un dato a un'altra base, non risolve conflitti tra fonti, non estende la tassonomia senza approvazione.</t>
+          <t>Non stima, non interpola, non media, non estrapola, non applica rendimenti o COP per riportare un dato a un'altra base, non risolve conflitti tra fonti, non estende la tassonomia senza approvazione, non promuove a validated.</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cosa l'agent NON scrive</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>'crediti generati', 'crediti prodotti', 'conversione in crediti di carbonio'; e 'certificato', 'conforme', 'validato da ente terzo', 'accreditato' riferiti alla libreria. Formulazione corretta: curata internamente, validata dal CSO (§11).</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>RIGA DI ESEMPIO — formato atteso, NON un record della libreria</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Valore di esempio</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Formato</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>factor_id</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>LIB05-S1-GASNAT-0001</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Prefisso libreria + scope + attivita' + progressivo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>factor_id</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>LIB05-S1-GASNAT-0001</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Uno tra: draft | in_review | validated | superseded | rejected</t>
+          <t>Prefisso libreria + scope + attivita' + progressivo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>1.9982</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Punto decimale, nessuna unita' nella cella del valore</t>
+          <t>Uno tra: draft | in_review | validated | superseded | rejected</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>unit_numerator / unit_denominator</t>
+          <t>value</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>kgCO2e   /   Sm3</t>
+          <t>1.9982</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Due celle distinte, nomenclatura da taxonomy/units.yaml</t>
+          <t>Punto decimale, nessuna unita' nella cella del valore</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>gas / gwp_set</t>
+          <t>unit_numerator / unit_denominator</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CO2e   /   IPCC AR6 GWP100</t>
+          <t>kgCO2e   /   Sm3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Set GWP identico su tutta la versione (gate G1)</t>
+          <t>Due celle distinte, nomenclatura da taxonomy/units.yaml</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>record_type</t>
+          <t>gas / gwp_set</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>emission_factor</t>
+          <t>CO2e   /   IPCC AR6 GWP100</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Determina il regime di validazione</t>
+          <t>Set GWP identico su tutta la versione (gate G1)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>valid_from / valid_to</t>
+          <t>record_type</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01   /   2026-12-31</t>
+          <t>emission_factor</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ISO 8601. Risoluzione per data di competenza del dato di attivita'</t>
+          <t>Determina il regime di validazione</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>source_table / source_page</t>
+          <t>valid_from / valid_to</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Tab. 2.3   /   p. 41</t>
+          <t>2026-01-01   /   2026-12-31</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Senza questi due campi il record non e' ammissibile</t>
+          <t>ISO 8601. Risoluzione per data di competenza del dato di attivita'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>extraction_method</t>
+          <t>source_table / source_page</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>manual_transcription</t>
+          <t>Tab. 2.3   /   p. 41</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Se manual_transcription -&gt; il record e' automaticamente T1</t>
+          <t>Senza questi due campi il record non e' ammissibile</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>manual_transcription</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Se manual_transcription -&gt; il record e' automaticamente T1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>license_class</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>VERDE | GIALLO | ROSSO; indeterminata = ROSSO</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>I valori della riga di esempio sono illustrativi del FORMATO e non sono fattori: non copiarli in un foglio libreria. Nessun valore di esempio e' stato inserito nei fogli 04-07 proprio per evitare che un numero non tracciato venga confuso con un record curato.</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="21" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="n"/>
-      <c r="C29" s="23" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="26" t="n"/>
-    </row>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A28:C30"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A29:C31"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2857,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2881,7 +2857,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ricerca eseguita per LOCALIZZARE i documenti primari. Nessun valore e' stato estratto da fonti secondarie: §1 vieta blog, articoli divulgativi, siti di ESCo e output di modelli linguistici come fonte. Tutti i record restano status = draft.</t>
+          <t>Ricerca eseguita per LOCALIZZARE i documenti primari. Nessun valore estratto da fonti secondarie: §1 vieta blog, articoli divulgativi, siti di ESCo, altri software di calcolo e output di modelli linguistici come fonte. Tutti i record restano status = draft.</t>
         </is>
       </c>
     </row>
@@ -2968,14 +2944,14 @@
           <t>Valore verbatim; articolo/comma; allegato e tabella; pagina; data di adozione; data di entrata in vigore; testo integrale per hash SHA-256</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>BLOCCATO — policy di egress</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Titolo del provvedimento coerente con quello citato in CLAUDE.md. La DATA di adozione risulta discordante tra fonti secondarie (20 / 28 / 31 marzo 2008): vedi CONF-001. Il valore non e' confermato: la conferma richiede il testo del provvedimento.</t>
+          <t>Titolo del provvedimento coerente con quello citato in CLAUDE.md. La DATA di adozione risulta discordante tra fonti secondarie (20 / 28 / 31 marzo 2008): CONF-001. Il valore non e' confermato.</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2973,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Atto non ancora identificato. Ipotesi da verificare in ordine: (a) Delibera EEN 3/08 e successivi aggiornamenti; (b) Allegato A alla delibera EEN 9/10 e successive Linee guida ARERA; (c) tabella dei coefficienti nella Guida Operativa GSE vigente; (d) D.M. 20 luglio 2004</t>
+          <t>Atto NON identificato. Ipotesi da verificare in ordine: (a) Delibera EEN 3/08 e successivi aggiornamenti; (b) Allegato A alla delibera EEN 9/10 e successive linee guida ARERA; (c) tabella dei coefficienti nella Guida Operativa GSE vigente; (d) D.M. 20 luglio 2004</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -3015,14 +2991,14 @@
           <t>Identificare l'atto che fissa il coefficiente; poi valore verbatim, tabella, pagina, vigenza</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>BLOCCATO — policy di egress</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Il valore circola in moduli di conversione di amministrazioni pubbliche, che NON sono fonte primaria: sono applicazioni di un coefficiente stabilito altrove. Resta GAP-002: l'atto non e' identificato, il record non supera i gate 2 e 10.</t>
+          <t>Il valore circola in moduli di conversione di amministrazioni pubbliche, che NON sono fonte primaria: sono applicazioni di un coefficiente stabilito altrove. GAP-002 resta aperto.</t>
         </is>
       </c>
     </row>
@@ -3054,22 +3030,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>https://www.gazzettaufficiale.it (ricerca per D.M. 20 luglio 2004)</t>
+          <t>https://www.gazzettaufficiale.it (ricerca per D.M. 20 luglio 2004) ; https://eur-lex.europa.eu (dir. 2012/27/UE, allegato IV)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Testo che fissa il fattore; articolo; allegato; pagina di GU; data di entrata in vigore</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
+          <t>Testo che fissa il fattore; articolo; allegato; pagina di GU; data di entrata in vigore. In parallelo l'allegato IV della direttiva per il confronto</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>BLOCCATO — policy di egress</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>CONFLITTO APERTO con la definizione IEA/OCSE e con la direttiva 2012/27/UE (41,868 GJ): vedi CONF-002. Non risolto dall'agent.</t>
+          <t>CONFLITTO APERTO con la definizione IEA/OCSE e con la direttiva 2012/27/UE (41,868 GJ): CONF-002. Non risolto dall'agent.</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3067,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>D.M. MASE 21 luglio 2025 (indicato da fonti secondarie come pubblicato in Gazzetta Ufficiale n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025). Guida Operativa attuativa approvata con decreto direttoriale (n. 203 del 28 luglio 2026 secondo fonti secondarie)</t>
+          <t>D.M. MASE 21 luglio 2025 (indicato da fonti secondarie come pubblicato in GU n. 211 dell'11 settembre 2025, applicabile ai progetti presentati dal 12 settembre 2025). Guida Operativa attuativa approvata con decreto direttoriale successivo</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -3109,14 +3085,14 @@
           <t>Testo integrale del decreto e degli allegati tecnici; articoli su vita utile, metodi di valutazione (consuntivo / standardizzato / semplificato), progetti aggregati; mappatura dei record LIB-01 impattati</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>BLOCCATO — policy di egress</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>ESCALATION A TOBIA (§14): se confermato, questo decreto ridefinisce la base normativa dell'intera LIB-01 e non e' un aggiornamento di singoli record. Nessun consolidamento di LIB-01 prima della verifica in Gazzetta Ufficiale.</t>
+          <t>PRIORITA' 1 ED ESCALATION A TOBIA (§14): se confermato, ridefinisce la base normativa dell'INTERA LIB-01, non aggiorna singoli record. Verificare questo PRIMA dei singoli coefficienti, altrimenti si rischia di verificarli contro un regime superato.</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3104,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Trasversale</t>
+          <t>GAP-004 / GAP-005</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Coefficienti per gli altri vettori ammessi; parametri CAR; vita utile; coefficienti di durabilita'; soglie di accesso</t>
+          <t>Coefficienti per gli altri vettori ammessi; parametri CAR; vita utile; coefficienti di durabilita'; soglie di accesso; PCI dei combustibili</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Guida Operativa GSE vigente e allegati (chiarimenti, guide settoriali, chiarimenti sulla Tabella 1 degli interventi)</t>
+          <t>Guida Operativa GSE vigente e allegati (chiarimenti operativi, guide settoriali, chiarimenti sulla tabella degli interventi)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3156,20 +3132,31 @@
           <t>Tabelle complete dei coefficienti, con edizione e data di pubblicazione</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>BLOCCATO — policy di egress</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Copertura non avviata: GAP-004. La verifica non e' iniziabile senza accesso al sito GSE.</t>
-        </is>
-      </c>
-    </row>
+          <t>Copertura non avviata. La verifica non e' iniziabile senza accesso al sito GSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>METODO. La ricerca (WebSearch) passa dall'API Anthropic e funziona; il fetch diretto dei documenti e' bloccato. Poiche' l'estrazione verbatim richiede il documento, la ricerca e' stata usata solo per identificare titolo, ente e posizione degli atti. Nessuno snippet di ricerca e' stato trattato come fonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
   </sheetData>
-  <mergeCells count="2">
+  <autoFilter ref="A4:I9"/>
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A11:I13"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3182,7 +3169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3190,7 +3177,7 @@
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3205,7 +3192,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Entrambi i valori sono riportati con la loro provenienza. La gerarchia di fonte va registrata da Garbin in taxonomy/source_hierarchy.yaml prima di qualunque scelta.</t>
+          <t>Entrambi i valori sono riportati con la loro provenienza. La gerarchia va registrata da Garbin in taxonomy/source_hierarchy.yaml prima di qualunque scelta.</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3266,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Il campo legal_reference di LIB-01 richiede la data di entrata in vigore. Una data errata rende il riferimento normativo non verificabile in audit di terza parte.</t>
+          <t>Il campo legal_reference di LIB-01 richiede la data di entrata in vigore. Una data errata rende il riferimento non verificabile in audit di terza parte.</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -3306,12 +3293,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>1 tep = 41,860 GJ  -&gt;  11.627,8 kWh_th (arrotondato a 11.628). Provenienza indicata: D.M. 20 luglio 2004, regime TEE italiano. DA VERIFICARE IN GU.</t>
+          <t>1 tep = 41,860 GJ -&gt; 11.627,8 kWh_th (arrotondato a 11.628). Provenienza indicata: D.M. 20 luglio 2004, regime TEE italiano. DA VERIFICARE IN GU.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>1 tep = 41,868 GJ  -&gt;  11.630 kWh_th. Provenienza indicata: definizione IEA/OCSE, ripresa dalla direttiva 2012/27/UE. DA VERIFICARE IN EUR-LEX.</t>
+          <t>1 tep = 41,868 GJ -&gt; 11.630 kWh_th. Provenienza indicata: definizione IEA/OCSE, ripresa dalla direttiva 2012/27/UE. DA VERIFICARE IN EUR-LEX.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -3321,7 +3308,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Numericamente marginale, ma NON trascurabile per la riproducibilita': un auditor che ricalcola con 41,868 non riproduce un risparmio calcolato con 41,860. Impatta anche la collocazione del record (LIB-01 regime TEE vs LIB-02 identita' fisica).</t>
+          <t>Numericamente marginale, e proprio per questo insidioso: troppo piccolo per essere notato come errore, troppo grande per essere zero. Un auditor che ricalcola con 41,868 non riproduce un risparmio calcolato con 41,860. Impatta anche la collocazione del record (LIB-01 regime TEE vs LIB-02 identita' fisica).</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -3335,10 +3322,1291 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>NOTA DI COERENZA INTERNA. L'11.628 kWh_th citato in CLAUDE.md e' aritmeticamente coerente con 41,860 GJ (41,860/0,0036 = 11.627,8): su questo il documento di governance e' internamente consistente. Il conflitto e' con la definizione internazionale, non interno al documento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A8:H10"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Allowlist dei domini di fonte primaria — rimedio a GAP-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sola lettura di documenti pubblici. La policy di rete e' attributo dell'environment (Default — trusted network access): non modificabile da dentro una sessione. Dettaglio in docs/ATL_OPS_EF_Allowlist_fonti_v1.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dominio</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Librerie servite</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Cosa serve</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Classe di licenza attesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>arera.it</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ARERA (gia' AEEG)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>LIB-01, LIB-02</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Delibera EEN 3/08 e allegati; linee guida e aggiornamenti dei coefficienti (VF-001, CONF-001)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>VERDE — atti normativi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>gazzettaufficiale.it</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Istituto Poligrafico dello Stato</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>LIB-01, LIB-02</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>D.M. MASE 21 luglio 2025 (VF-004); D.M. 20 luglio 2004 (VF-003)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>VERDE — atti normativi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>gse.it</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>GSE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>LIB-01, LIB-02</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Guida Operativa certificati bianchi e allegati: chiarimenti, guide settoriali, tabella degli interventi, coefficienti (VF-002, VF-005)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>mase.gov.it</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MASE</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>LIB-01</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Decreti e provvedimenti su efficienza energetica, TEE, CAR</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>mimit.gov.it</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MIMIT (gia' MISE)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>LIB-01</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Guide operative e decreti attuativi storici</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>eur-lex.europa.eu</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Unione Europea</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>LIB-02, LIB-05, IP</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Direttiva 2012/27/UE allegato IV (CONF-002); direttiva 2024/825; direttiva 96/9/CE per la nota IP §15</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>isprambiente.gov.it</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ISPRA</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>LIB-05</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Inventario nazionale dei gas serra e fattori di emissione per l'Italia — fonte gerarchicamente prevalente (§4)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>efficienzaenergetica.enea.it</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ENEA</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>LIB-02</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Diagnosi energetiche UNI CEI 11339 e parametri di riferimento</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>eea.europa.eu</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>European Environment Agency</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>LIB-05</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Fattori europei e geografie non coperte dall'inventario nazionale</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>ipcc-nggip.iges.or.jp</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>IPCC — National GHG Inventories Programme</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>LIB-05</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Linee guida IPCC ed Emission Factor Database; set GWP (gate G1)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>VERDE — linee guida IPCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>ghgprotocol.org</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>GHG Protocol</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>LIB-05</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Standard e categorie Scope 3. Aggiornamenti STRUTTURALI -&gt; escalation immediata (§6)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>VERDE — da verificare i termini</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>efrag.org</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>EFRAG</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>LIB-05</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>ESRS. Aggiornamenti che modificano la struttura -&gt; escalation (§6)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>joint-research-centre.ec.europa.eu</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>JRC</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>LIB-06</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Dataset di riferimento europei</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>environment.ec.europa.eu</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Commissione europea — DG ENV</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>LIB-06</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Product / Organisation Environmental Footprint</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>environdec.com</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>EPD International</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>LIB-06</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>EPD verificate con numero di registrazione e organismo di verifica</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>GIALLO — quarantena, nessun rilascio senza conferma scritta di Tobia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>eco-platform.org</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ECO Platform</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>LIB-06</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>EPD europee</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>GIALLO — stesso regime</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>verra.org</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Verra</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>LIB-03, LIB-04</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Metodologie VCS, buffer di non-permanenza, leakage, requisiti di monitoraggio</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VERDE — da verificare i termini</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>registry.verra.org</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Verra</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>LIB-03, LIB-04</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Registro dei progetti</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>VERDE — da verificare i termini</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>goldstandard.org</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Gold Standard</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LIB-03, LIB-04</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Metodologie e requisiti</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>VERDE — da verificare i termini</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>globalgoals.goldstandard.org</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Gold Standard</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>LIB-03, LIB-04</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Registro</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>VERDE — da verificare i termini</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>crea.gov.it</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>CREA</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LIB-04</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Interlocuzione forestale, parametri biometrici, registro agroforestale</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>WILDCARD SUI SOTTODOMINI — NON OPZIONALE. ARERA e GSE servono i PDF da percorsi e host distinti da quello della pagina indice. Autorizzare *.arera.it, *.gse.it, *.gazzettaufficiale.it, *.mase.gov.it, *.mimit.gov.it, *.europa.eu. Senza wildcard il fetch della pagina riesce e quello dell'allegato no: e' il caso peggiore, perche' sembra funzionare e non produce provenienza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>NOTA LIB-04. Il dominio del registro pubblico dei crediti agroforestali NON e' indicato: va confermato al tavolo CREA invece che ipotizzato. Scriverlo per ipotesi in un documento operativo sarebbe la stessa classe di errore dei coefficienti non tracciati. Vale la nota di coordinamento del §3: le specifiche vanno allineate a quel tavolo PRIMA di consolidare la tassonomia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>COME APPLICARLA. 1) In claude.ai/code aprire le impostazioni dell'environment Default. 2) Sostituire il preset di rete con una policy che includa il Tier 1 (Tier 2 e 3 quando si aprono le rispettive librerie). 3) Avviare una NUOVA sessione: la policy si applica all'avvio del container. Riferimento: https://code.claude.com/docs/en/claude-code-on-the-web</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+  </sheetData>
+  <autoFilter ref="A4:F25"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A27:F29"/>
+    <mergeCell ref="A31:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="86" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Domini che NON vanno autorizzati</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Autorizzarli non serve e crea un rischio di contaminazione che non si sana a valle (§5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Esempi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Classe</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Perche' e cosa fare invece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Norme tecniche a pagamento</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>store.uni.com, iso.org e simili</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>ROSSA — contenuti dietro paywall</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Vanno acquistate come documenti, non scaricate; la citazione dei valori e' vietata. L'esistenza si registra in gaps/licensed_sources.md come opzione di licensing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Database LCA commerciali</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Banche dati proprietarie di software LCA, dataset a pagamento di agenzie internazionali</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>ROSSA — divieto assoluto</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Non scaricare, non estrarre, non citare valori. Se servono per coprire una lacuna materiale: scheda con costo, lacuna coperta e impatto sui clienti attivi, poi STOP ed escalation a Tobia (§14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Portali di settore, blog, siti di ESCo, altri software di calcolo, enciclopedie collaborative</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Vietati come FONTE dal §1</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Utili solo per LOCALIZZARE un documento, e per quello WebSearch gia' basta. Autorizzarli al fetch aumenta solo la probabilita' che un valore non tracciato entri in un record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fonti a licenza non determinabile</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>ROSSA per default (§5)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Nessuna ingestione. Il dubbio si risolve verso il divieto, non verso la completezza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Questo gate ha priorita' su completezza e scadenze (§5). La libreria viaggia dentro una licenza commerciale B.R.A.I.N.: un dataset non redistribuibile che entra qui non si toglie piu' a valle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A10:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Piano di lavoro — alla prima sessione con allowlist attiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L'ordine non e' quello dei numeri: la priorita' e' condizionata dal decreto 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Attivita'</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Domini necessari</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Output atteso</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Perche' in questa posizione</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Dipendenze</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>VF-004 — D.M. MASE 21 luglio 2025 in Gazzetta Ufficiale</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>gazzettaufficiale.it, gse.it</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Conferma di esistenza, data, numero di GU; articoli su vita utile, metodi di valutazione, progetti aggregati; elenco dei record LIB-01 impattati</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>PRIMA DI TUTTO IL RESTO. Se confermato, ridefinisce la base normativa dell'intera LIB-01: verificare i singoli coefficienti prima significherebbe rischiare di validarli contro un regime superato. Esito -&gt; ESCALATION A TOBIA (§14), non aggiornamento di record.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Nessuna oltre l'allowlist Tier 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>VF-001 — Delibera EEN 3/08</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>arera.it</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Valore verbatim, articolo, allegato, tabella, pagina, data di adozione e di entrata in vigore; file archiviato con SHA-256</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Chiude CONF-001. Il record LIB01-EE-PRIM-0001 puo' passare a in_review. Attenzione a non collassare l'asimmetria: e' energia primaria, non identita' fisica.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Esito di VF-004 (per sapere se il coefficiente e' ancora vigente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>VF-002 — atto che fissa il coefficiente gas naturale</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>arera.it, gse.it, gazzettaufficiale.it</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Identificazione dell'atto; poi valore verbatim, tabella, pagina, vigenza</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Se l'atto non esiste, la lacuna resta e va dichiarata: e' un esito legittimo e va scritto, non aggirato.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Esito di VF-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>VF-003 — D.M. 20 luglio 2004 e allegato IV dir. 2012/27/UE</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>gazzettaufficiale.it, eur-lex.europa.eu</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Entrambi i testi, per portare CONF-002 a Garbin con i documenti in mano invece che con due citazioni</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Non risolvere il conflitto: presentarlo. La decisione di gerarchia e' del CSO e va registrata in taxonomy/source_hierarchy.yaml.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Nessuna</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>VF-005 — Guida Operativa GSE e allegati</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>gse.it</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Tabelle complete dei coefficienti per gli altri vettori, parametri CAR, vita utile, durabilita', soglie di accesso, PCI</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Copre GAP-004 e parte di GAP-005. Volume potenzialmente &gt; 50 record: spezzare in pacchetti sequenziali per materialita' (§9).</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Esito di VF-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Deposito e hash</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>sources/&lt;org&gt;/&lt;documento&gt;_&lt;edizione&gt;/ con source_file_sha256 per ogni documento; retrieval_date compilata</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>E' la condizione del gate 2 e del gate 14. Senza questo passaggio nessun record e' promuovibile, anche con i valori in mano.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Passi 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Tassonomia minima</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>taxonomy/units.yaml (regole di conversione dichiarate), plausibility_ranges.yaml, source_hierarchy.yaml registrata da Garbin</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Sblocca i gate 3, 4 e 6. GAP-013. Senza units.yaml nessuna conversione e' ammissibile, quindi il lavoro sui valori non si chiude comunque.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Decisioni di Garbin su gerarchia</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Primo pacchetto di validazione</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>validation/ATL_OPS_EF_Pacchetto_LIB01_&lt;versione&gt;/ con sintesi.md, diff.xlsx, conflitti.md, gaps.md, sources/</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Tetto 50 record. Tutti i record LIB-01 sono T1: validazione puntuale. Solo dopo la firma di Garbin si rilascia, e solo gli approvati.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Passi 1-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>COSA RESTA FUORI DA QUESTO PIANO. LIB-03 e LIB-04 non partono con l'allowlist: dipendono dall'allineamento al tavolo CREA (GAP-007) e dalla scelta dello standard di certificazione per progetto, che e' una decisione di business, non di curazione. LIB-06 e' limitata strutturalmente dalla licenza dei dati di background (GAP-012): serve una decisione di Tobia sull'acquisto, non piu' lavoro di ricerca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A14:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3373,7 +4641,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Gruppo</t>
@@ -4219,7 +5487,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Regola di conversione dichiarata in taxonomy/units.yaml. 'n/a' se nessuna.</t>
+          <t>Regola dichiarata in taxonomy/units.yaml. 'n/a' se nessuna.</t>
         </is>
       </c>
     </row>
@@ -4432,6 +5700,300 @@
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Registro dello sforzo di curazione (§15) — da riversare in docs/changelog.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Prova d'investimento per il diritto sui generis sulla banca dati (dir. 96/9/CE; art. 102-bis L. 633/1941). Ricostruirlo a posteriori non e' possibile: tenuto dal primo commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Attivita' di curazione</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Record lavorati</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Fonti verificate</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Lacune censite (cum.)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Conflitti aperti (cum.)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6c55b4e</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Collocazione del documento di governance ATL_OPS_AgentEF_IstruzioniClaudeCode_v2 come CLAUDE.md in root, riportato verbatim</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1 documento normalizzato</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>c71af4b</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Costruzione del workbook: schema canonico a 50 campi, 6 template libreria, semaforo licenze, 14 gate, gate trasversali G1-G3, tier di validazione, legenda</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>3 record bozza trascritti (tutti manual_transcription, quindi tutti T1)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>d064cfd</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Verifica di fonte: 6 query di ricerca, localizzazione dei documenti primari, apertura dei conflitti</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>3 record rivisti (NOTA_CURATORE aggiornata)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>4 documenti primari localizzati, 0 scaricati (egress)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>94026e4</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Allowlist dei domini di fonte primaria: docs/ATL_OPS_EF_Allowlist_fonti_v1.md, 21 domini su 3 tier, 4 categorie escluse</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>(questo commit)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Ricostruzione completa del workbook a 20 fogli: integrati allowlist, domini esclusi, piano di lavoro in 8 passi e questo registro. Stato dei 14 gate esplicitato record per record</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>3 record confermati draft</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>COLONNA ORE NON COMPILATA, DELIBERATAMENTE. L'agent non ha modo di misurare il tempo-persona impiegato e non lo stima: sarebbe un numero inventato dentro il documento che deve dimostrare un investimento. Va compilata da chi lavora. Se la dimostrazione dell'investimento e' rilevante per la tutela sui generis, questa colonna e' la parte che conta di piu' ed e' l'unica che l'agent non puo' produrre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Metrica di successo dell'agent (§0): quota di record approvati da Garbin senza rilievi; record entrati in produzione senza firma, che deve essere ZERO. Stato al 21/08/2026: record approvati 0 su 0 presentati; record in produzione senza firma 0. La seconda metrica e' rispettata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:H13"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A15:H17"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4459,7 +6021,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -4502,95 +6064,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -4843,26 +6361,26 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>LIB-01 — Coefficienti TEE / GSE. Regime normativo puro: si aggiorna solo per modifica di legge. legal_reference obbligatorio (gate 10). Tutti i record sono T1 (validazione puntuale, record per record). Sorveglianza: Gazzetta Ufficiale, portale GSE, ARERA — non la letteratura.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>LIB-01 — Coefficienti TEE / GSE. Regime normativo puro: si aggiorna solo per modifica di legge. legal_reference obbligatorio (gate 10). Tutti i record sono T1. Sorveglianza: Gazzetta Ufficiale, portale GSE, ARERA — non la letteratura.</t>
         </is>
       </c>
     </row>
@@ -5050,7 +6568,7 @@
       </c>
       <c r="AN5" s="4" t="inlineStr">
         <is>
-          <t>0,187 x 10^-3 tep/kWh = 0,187 tep/MWh. Equivalenza citata in CLAUDE.md: 1 tep = 5.347,6 kWh_el (reciproco, da non usare come record autonomo senza regola in units.yaml).</t>
+          <t>0,187 x 10^-3 tep/kWh = 0,187 tep/MWh. Equivalenza citata in CLAUDE.md: 1 tep = 5.347,6 kWh_el (reciproco: non usare come record autonomo senza regola in units.yaml).</t>
         </is>
       </c>
       <c r="AO5" s="4" t="inlineStr">
@@ -5089,7 +6607,7 @@
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="4" t="inlineStr">
         <is>
-          <t>ATTENZIONE ASIMMETRIA (§3 LIB-01): questo valore incorpora il rendimento medio del parco termoelettrico nazionale (~46%) — e' un fattore di ENERGIA PRIMARIA, non un'identita' fisica. Non trattarlo come oggetto omogeneo rispetto al tep-&gt;kWh_th. Valore riportato in CLAUDE.md come verificato ad agosto 2026 e da riconfermare in fonte primaria prima del rilascio.  || VERIFICA DI FONTE 21/08/2026 (VF-001): individuato il provvedimento ARERA corrispondente al titolo citato, ma il sito e' inaccessibile (GAP-018) e la data di adozione risulta discordante tra fonti secondarie (CONF-001). Il valore NON e' confermato in fonte primaria: il record resta draft.</t>
+          <t>ASIMMETRIA DA NON COLLASSARE (§3 LIB-01): il valore incorpora il rendimento medio del parco termoelettrico nazionale (~46%) — e' un fattore di ENERGIA PRIMARIA, non un'identita' fisica. Non trattarlo come oggetto omogeneo rispetto al tep-&gt;kWh_th. || VERIFICA DI FONTE 21/08/2026 (VF-001): individuato il provvedimento ARERA con titolo corrispondente, sito inaccessibile (GAP-018), data di adozione discordante tra fonti secondarie (CONF-001). Valore NON confermato in fonte primaria: resta draft.</t>
         </is>
       </c>
       <c r="AZ5" s="4" t="inlineStr"/>
@@ -5243,7 +6761,7 @@
       </c>
       <c r="AF6" s="4" t="inlineStr">
         <is>
-          <t>Tabelle di conversione ufficiali — [DA VERIFICARE IN FONTE PRIMARIA] identificare l'atto esatto</t>
+          <t>Atto non identificato — [DA VERIFICARE IN FONTE PRIMARIA]</t>
         </is>
       </c>
       <c r="AG6" s="4" t="inlineStr">
@@ -5318,7 +6836,7 @@
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr">
         <is>
-          <t>La fonte indicata in CLAUDE.md ('Tabelle di conversione ufficiali') non e' localizzabile a documento/edizione/tabella/pagina. Il record NON supera il gate 2 (provenienza completa) ne' il gate 10: non entra in un pacchetto di validazione fino a identificazione dell'atto.  || VERIFICA DI FONTE 21/08/2026 (VF-002): ricerca eseguita, atto NON identificato. Il coefficiente compare solo in moduli applicativi di enti pubblici, che sono applicazioni e non fonte primaria. Il record resta draft e fuori pacchetto.</t>
+          <t>VERIFICA DI FONTE 21/08/2026 (VF-002): ricerca eseguita, l'atto che fissa il coefficiente NON e' stato identificato. Il valore compare in moduli di conversione di amministrazioni pubbliche, che sono APPLICAZIONI di un coefficiente stabilito altrove, non la fonte che lo stabilisce. Il record non supera i gate 2 e 10: resta draft e fuori da qualunque pacchetto. Se non esiste un atto che lo fissa, la lacuna resta e va dichiarata: e' un esito legittimo.</t>
         </is>
       </c>
       <c r="AZ6" s="4" t="inlineStr"/>
@@ -5364,7 +6882,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -5407,95 +6925,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -5748,24 +7222,24 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>LIB-02 — Conversioni energetiche e parametri di riferimento. Regola dura: i parametri di rendimento (generatori, COP/SCOP, rendimenti di distribuzione, perdite di rete) sono record SEPARATI, mai moltiplicati insieme in un valore precompilato. Il motore combina; la libreria espone i termini singoli.</t>
         </is>
@@ -5914,12 +7388,12 @@
       </c>
       <c r="AE5" s="4" t="inlineStr">
         <is>
-          <t>[DA VERIFICARE IN FONTE PRIMARIA]</t>
+          <t>MASE (gia' Ministero delle Attivita' Produttive)</t>
         </is>
       </c>
       <c r="AF5" s="4" t="inlineStr">
         <is>
-          <t>Definizione tep — [DA VERIFICARE IN FONTE PRIMARIA]</t>
+          <t>D.M. 20 luglio 2004 — [DA VERIFICARE IN FONTE PRIMARIA]</t>
         </is>
       </c>
       <c r="AG5" s="4" t="inlineStr">
@@ -5955,7 +7429,7 @@
       </c>
       <c r="AN5" s="4" t="inlineStr">
         <is>
-          <t>Identita' pura, nessun rendimento incorporato. Equivalenza citata in CLAUDE.md: 1 tep = 11.628 kWh_th.</t>
+          <t>Identita' pura, nessun rendimento incorporato. Equivalenza citata in CLAUDE.md: 1 tep = 11.628 kWh_th (41,860/0,0036).</t>
         </is>
       </c>
       <c r="AO5" s="4" t="inlineStr">
@@ -5994,7 +7468,7 @@
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="4" t="inlineStr">
         <is>
-          <t>DECISIONE DI CLASSIFICAZIONE DA CONFERMARE A GARBIN: CLAUDE.md cita questo valore nella tabella di riferimento di LIB-01, ma §3 LIB-02 assegna a LIB-02 la catena tep&lt;-&gt;GJ&lt;-&gt;kWh&lt;-&gt;Sm3 come identita' pura. Collocato qui in via provvisoria. L'11.628 kWh_th/tep non incorpora alcun rendimento: non e' omogeneo allo 0,187 tep/kWh di LIB-01.  || VERIFICA DI FONTE 21/08/2026 (VF-003): candidato primario D.M. 20 luglio 2004 (da confermare in GU). CONFLITTO CONF-002 con la definizione IEA/OCSE e con la direttiva 2012/27/UE (41,868 GJ -&gt; 11.630 kWh_th). Non risolto: decisione di gerarchia a Garbin.</t>
+          <t>DECISIONE DI CLASSIFICAZIONE A GARBIN: CLAUDE.md cita questo valore nella tabella di riferimento di LIB-01, ma §3 LIB-02 assegna a LIB-02 la catena tep&lt;-&gt;GJ&lt;-&gt;kWh&lt;-&gt;Sm3 come identita' pura. Collocato qui in via provvisoria. L'11.628 kWh_th/tep non incorpora alcun rendimento: non e' omogeneo allo 0,187 tep/kWh di LIB-01. || VERIFICA DI FONTE 21/08/2026 (VF-003): candidato primario D.M. 20 luglio 2004, da confermare in GU. CONFLITTO CONF-002 con la definizione IEA/OCSE e la direttiva 2012/27/UE (41,868 GJ -&gt; 11.630 kWh_th). Non risolto.</t>
         </is>
       </c>
       <c r="AZ5" s="4" t="inlineStr"/>
@@ -6040,7 +7514,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -6083,95 +7557,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6424,26 +7854,26 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>LIB-03 — CarbonSense. Contiene parametri di METODOLOGIA (record_type = methodology_parameter), non fattori: metodologie applicabili, criteri di baseline e addizionalita', buffer di non-permanenza, detrazioni per leakage, requisiti di monitoraggio, periodo di accreditamento. Formulazione ammessa: 'tCO2e potenzialmente eleggibili secondo la metodologia X, soggette a validazione e verifica di ente terzo'.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>LIB-03 — CarbonSense. Parametri di METODOLOGIA (record_type = methodology_parameter), non fattori: metodologie applicabili, baseline e addizionalita', buffer di non-permanenza, leakage, requisiti di monitoraggio, periodo di accreditamento. Formulazione ammessa: 'tCO2e potenzialmente eleggibili secondo la metodologia X, soggette a validazione e verifica di ente terzo'.</t>
         </is>
       </c>
     </row>
@@ -6487,7 +7917,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -6530,95 +7960,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6871,26 +8257,26 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>LIB-04 — Forestale. Come LIB-03, piu' la componente biometrica (curve di accrescimento, densita' basale, fattori di espansione, rapporto radici/parte epigea, frazione di carbonio): sono MODELLI, non fattori. carbon_pool sempre dichiarato (gate 12): due stime su pool diversi non sono confrontabili. Allineare a CREA prima di consolidare la tassonomia. Blue carbon lagunare: pool e parametri propri, NON estensione dei modelli terrestri.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>LIB-04 — Forestale. Come LIB-03, piu' la componente biometrica (curve di accrescimento, densita' basale, fattori di espansione, rapporto radici/parte epigea, frazione di carbonio): sono MODELLI, non fattori. carbon_pool sempre dichiarato (gate 12). Allineare a CREA prima di consolidare la tassonomia. Blue carbon lagunare: pool e parametri propri, NON estensione dei modelli terrestri.</t>
         </is>
       </c>
     </row>
@@ -6934,7 +8320,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -6977,95 +8363,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7318,26 +8660,26 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>LIB-05 — Carbon Footprint di organizzazione. Scope 1 (combustione stazionaria e mobile, fuggitive F-gas, processo), Scope 2 (elettricita' location-based E market-based, teleriscaldamento, vapore — entrambi obbligatori per ogni geografia o assenza dichiarata in gaps), Scope 3 (15 categorie, distinguendo spend-based / average-data / supplier-specific). Disaggregare CO2/CH4/N2O dove la fonte lo fa: non aggregare cio' che la fonte separa.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>LIB-05 — Carbon Footprint di organizzazione. Scope 1 (combustione stazionaria e mobile, fuggitive F-gas, processo), Scope 2 (location-based E market-based, teleriscaldamento, vapore — entrambi o assenza dichiarata), Scope 3 (15 categorie, distinte spend-based / average-data / supplier-specific). Disaggregare CO2/CH4/N2O dove la fonte lo fa.</t>
         </is>
       </c>
     </row>
@@ -7381,7 +8723,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -7424,95 +8766,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>IDENTIFICAZIONE</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>CLASSIFICAZIONE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>VALORE</t>
         </is>
       </c>
-      <c r="Q1" s="27" t="n"/>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="27" t="n"/>
-      <c r="T1" s="27" t="n"/>
-      <c r="U1" s="27" t="n"/>
-      <c r="V1" s="27" t="n"/>
-      <c r="W1" s="27" t="n"/>
-      <c r="X1" s="28" t="n"/>
-      <c r="Y1" s="11" t="inlineStr">
+      <c r="Y1" s="12" t="inlineStr">
         <is>
           <t>NATURA DEL RECORD</t>
         </is>
       </c>
-      <c r="Z1" s="11" t="inlineStr">
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>VIGENZA</t>
         </is>
       </c>
-      <c r="AA1" s="27" t="n"/>
-      <c r="AB1" s="27" t="n"/>
-      <c r="AC1" s="27" t="n"/>
-      <c r="AD1" s="28" t="n"/>
-      <c r="AE1" s="11" t="inlineStr">
+      <c r="AE1" s="12" t="inlineStr">
         <is>
           <t>PROVENIENZA</t>
         </is>
       </c>
-      <c r="AF1" s="27" t="n"/>
-      <c r="AG1" s="27" t="n"/>
-      <c r="AH1" s="27" t="n"/>
-      <c r="AI1" s="27" t="n"/>
-      <c r="AJ1" s="27" t="n"/>
-      <c r="AK1" s="27" t="n"/>
-      <c r="AL1" s="27" t="n"/>
-      <c r="AM1" s="27" t="n"/>
-      <c r="AN1" s="27" t="n"/>
-      <c r="AO1" s="27" t="n"/>
-      <c r="AP1" s="28" t="n"/>
-      <c r="AQ1" s="11" t="inlineStr">
+      <c r="AQ1" s="12" t="inlineStr">
         <is>
           <t>LICENZA</t>
         </is>
       </c>
-      <c r="AR1" s="27" t="n"/>
-      <c r="AS1" s="28" t="n"/>
-      <c r="AT1" s="11" t="inlineStr">
+      <c r="AT1" s="12" t="inlineStr">
         <is>
           <t>VALIDAZIONE</t>
         </is>
       </c>
-      <c r="AU1" s="27" t="n"/>
-      <c r="AV1" s="27" t="n"/>
-      <c r="AW1" s="27" t="n"/>
-      <c r="AX1" s="28" t="n"/>
-      <c r="AY1" s="12" t="inlineStr">
+      <c r="AY1" s="13" t="inlineStr">
         <is>
           <t>CAMPI DI LAVORO (non schema)</t>
         </is>
       </c>
-      <c r="AZ1" s="27" t="n"/>
-      <c r="BA1" s="28" t="n"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7765,26 +9063,26 @@
           <t>record_sha256</t>
         </is>
       </c>
-      <c r="AY2" s="13" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>NOTA_CURATORE</t>
         </is>
       </c>
-      <c r="AZ2" s="13" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>ESITO</t>
         </is>
       </c>
-      <c r="BA2" s="13" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>NOTA VALIDATORE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>LIB-06 — Carbon Footprint di prodotto. functional_unit e system_boundary obbligatori e non nullabili: senza questi due campi un PCF non e' confrontabile con nulla. Distinguere dati specifici (EPD verificata, con numero di registrazione e organismo di verifica) da dati generici di background. Priorita': costruzione, poi rifiuti/economia circolare, poi agroalimentare.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>LIB-06 — Carbon Footprint di prodotto. functional_unit e system_boundary obbligatori e non nullabili: senza questi due campi un PCF non e' confrontabile con nulla. Distinguere dati specifici (EPD verificata, con numero di registrazione e organismo di verifica) da dati generici di background.</t>
         </is>
       </c>
     </row>
@@ -7836,7 +9134,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Classe</t>
@@ -7864,7 +9162,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>VERDE</t>
         </is>
@@ -7891,7 +9189,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>GIALLO</t>
         </is>
@@ -7918,7 +9216,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ROSSO</t>
         </is>
@@ -7945,7 +9243,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>INDETERMINATA</t>
         </is>
